--- a/source_data/Additional_Figures.xlsx
+++ b/source_data/Additional_Figures.xlsx
@@ -39,7 +39,7 @@
     <t>Rows</t>
   </si>
   <si>
-    <t>Additional analyses (outputs/2026-10-08/additional/)</t>
+    <t>Additional analyses (outputs/additional/)</t>
   </si>
   <si>
     <t>Generated by pipelines/build_source_data.R</t>
